--- a/financial_models/output/Azalea_Hospice_Proforma_Rev4.10_DYNAMIC.xlsx
+++ b/financial_models/output/Azalea_Hospice_Proforma_Rev4.10_DYNAMIC.xlsx
@@ -7,20 +7,23 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Tower" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Census Waterfall" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; Runway" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Year Summary" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Budget" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Tower" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Census Waterfall" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; Runway" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Year Summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Budget" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Cash Flow &amp; Runway'!$1:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
     <numFmt numFmtId="169" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="170" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,8 +98,64 @@
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3B2D"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F3B5C"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -128,8 +187,13 @@
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1EC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -151,11 +215,16 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="001F3B2D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -262,6 +331,21 @@
     <xf numFmtId="170" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -633,1557 +717,1273 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F3864"/>
+    <tabColor rgb="001F3B2D"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N135"/>
+  <dimension ref="B2:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AZALEA HOSPICE - REFUGE OPERATING MODEL</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL TOWER - every number in the model flows from this tab. Yellow = input; everything else is formulas.</t>
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>AZALEA HOSPICE &amp; PALLIATIVE CARE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="37" t="inlineStr">
+        <is>
+          <t>Refuge Hospice, LLC Acquisition - Financial Proforma</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>COMPANY &amp; DEAL  (current Refuge structure)</t>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>Revision 4.10  |  July 2026  |  Tyler Hospice Hold, LLC (EIN 41-4966640)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Starting capital on deposit (equity)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Jim Bullard $195K + owner $55K</t>
-        </is>
-      </c>
+      <c r="B5" s="39" t="n"/>
+      <c r="C5" s="39" t="n"/>
+      <c r="D5" s="39" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Pre-opening / startup spend from capital</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>0 = funded elsewhere</t>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>Prepared for the SBA 7(a) application (SourceFunding / The Brownmiller Group) and company planning.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Refuge license purchase price (100% membership CHOW)</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Acct 1980 intangible</t>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>36 monthly periods (Jul-2026 to Jun-2029). Every calculated cell is a live formula; all inputs on the Control Tower.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Down payment at closing (Month 1)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>125000</v>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>REAL-CASH DISCIPLINE: no revolver or assumed facility anywhere in this model. Cash shortfalls, if any, are shown</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Seller monthly payment (MIPA 7/14/2026)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>31250</v>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>$31,250/mo Sep-Dec per executed MIPA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>First seller payment month</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>3 = September</t>
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>as UNFUNDED NEED - the amount of additional capital required - never plugged by a balancing facility.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Last seller payment month</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>6 = December</t>
-        </is>
-      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>HEADLINE METRICS (all cells below are live links)</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Seller note simple interest (APR)</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>0.06</v>
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>Net patient revenue - Year 1 / 2 / 3</t>
+        </is>
+      </c>
+      <c r="C12" s="45">
+        <f>'3-Year Summary'!B5</f>
+        <v/>
+      </c>
+      <c r="D12" s="45">
+        <f>'3-Year Summary'!C5</f>
+        <v/>
+      </c>
+      <c r="E12" s="45">
+        <f>'3-Year Summary'!D5</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Balloon month (36-month rule / January)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>7</v>
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>EBITDA (pre-debt-service) - Year 1 / 2 / 3</t>
+        </is>
+      </c>
+      <c r="C13" s="45">
+        <f>'3-Year Summary'!B6</f>
+        <v/>
+      </c>
+      <c r="D13" s="45">
+        <f>'3-Year Summary'!C6</f>
+        <v/>
+      </c>
+      <c r="E13" s="45">
+        <f>'3-Year Summary'!D6</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Balloon takeout note rate (APR)</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>BASE CASE: SBA/bank funds the Jan balloon; modeled at the conservative 6%/36 basis</t>
-        </is>
+      <c r="B14" s="44" t="inlineStr">
+        <is>
+          <t>Minimum cash across 36 months (base case)</t>
+        </is>
+      </c>
+      <c r="C14" s="45">
+        <f>'Cash Flow &amp; Runway'!B46</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Balloon takeout note term (months)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>36</v>
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>Peak additional capital required (base case)</t>
+        </is>
+      </c>
+      <c r="C15" s="45">
+        <f>'Cash Flow &amp; Runway'!B47</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>BANK-REFI TOGGLE (1 = $500K/6%/36 funds Sept - BASE)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>BASE = 1: Bullard-relationship bank refi (confirmed) pays seller Sept; 0 = seller carried to Jan balloon per MIPA</t>
-        </is>
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>Month-36 ending cash</t>
+        </is>
+      </c>
+      <c r="C16" s="45">
+        <f>'Cash Flow &amp; Runway'!AL43</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Full-refi funding month</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>3 = September</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Full-refi amount</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>500000</v>
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>Master integrity check (0 = clean)</t>
+        </is>
+      </c>
+      <c r="C17" s="46">
+        <f>'Checks'!B12</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Full-refi rate (APR)</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="B19" s="42" t="inlineStr">
+        <is>
+          <t>FINANCING SEQUENCE (Path A)</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Full-refi term (months)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n">
-        <v>36</v>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Aug 2026 - Equity ($250,000: J. Bullard $195K + G. Schackmann $55K) funds the $125,000 license down payment (49%)</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>SBA TOGGLE (1 = SBA 7(a) funds &amp; REFINANCES the bank note) - BASE</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>SBA proceeds pay off the bank-refi balance at funding month</t>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Sep 2026 - Interim bank note ($500,000, 6%, 36-mo) pays the sellers in full; surplus to working capital</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>SBA funding month</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>7 = January (51% transfer / 42 CFR 424.550(b) date)</t>
+      <c r="B22" s="47" t="inlineStr">
+        <is>
+          <t>Oct-Dec  - Bank note service $15,211/month; owner salaries deferred until break-even census (accrued, repaid Jan)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>SBA amount</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>500000</v>
+      <c r="B23" s="47" t="inlineStr">
+        <is>
+          <t>Jan 2027 - SBA 7(a) $500,000 funds at the 51% transfer (42 CFR 424.550(b)) and refinances the bank note</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>SBA rate (APR)</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>SBA term (months)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>10-year 7(a); ~$6,747/mo at 10.5%</t>
+      <c r="B24" s="47" t="inlineStr">
+        <is>
+          <t>Feb 2027 - Single SBA payment of $6,747/month (10.5%, 10-year); recurring coverage 3.8x / 8.6x / 12.2x</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>License intangible amortization (yrs, Acct 7200)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n">
-        <v>15</v>
-      </c>
+      <c r="B26" s="42" t="inlineStr">
+        <is>
+          <t>WORKBOOK CONTENTS</t>
+        </is>
+      </c>
+      <c r="C26" s="43" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>CHOW / go-live month (amortization starts)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>1</v>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Control Tower</t>
+        </is>
+      </c>
+      <c r="D27" s="49" t="inlineStr">
+        <is>
+          <t>Every model input - deal terms, census, rates, staffing, toggles (scenario, refi, SBA, deferral)</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>CENSUS  (admissions row lives on Census Waterfall - blue)</t>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Census Waterfall</t>
+        </is>
+      </c>
+      <c r="D28" s="49" t="inlineStr">
+        <is>
+          <t>Admissions, discharge waterfall, ADC, patient days</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Days per month (model uniform)</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n">
-        <v>30.4</v>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Revenue Model</t>
+        </is>
+      </c>
+      <c r="D29" s="49" t="inlineStr">
+        <is>
+          <t>CMS rate build, payer mix, net patient revenue</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Average length of stay (days)</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="n">
-        <v>82</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>drives discharges = BOM x days/ALOS</t>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Staffing</t>
+        </is>
+      </c>
+      <c r="D30" s="49" t="inlineStr">
+        <is>
+          <t>FTEs (census-driven with 1-month hire lag), payroll, PRN supplement, owner-deferral schedule</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Deaths as share of discharges</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n">
-        <v>0.55</v>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Operating Budget</t>
+        </is>
+      </c>
+      <c r="D31" s="49" t="inlineStr">
+        <is>
+          <t>Direct patient care, facility, G&amp;A, contingency</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>SCENARIO CASES  (1 = Base, 2 = Downside, 3 = Upside; active values are formulas)</t>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="D32" s="49" t="inlineStr">
+        <is>
+          <t>Accrual P&amp;L with account codes; EBITDA and margins</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE CASE</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>flip 1/2/3 - drives capture, payroll adj, CHOW hold</t>
+      <c r="B33" s="48" t="inlineStr">
+        <is>
+          <t>Cash Flow &amp; Runway</t>
+        </is>
+      </c>
+      <c r="D33" s="49" t="inlineStr">
+        <is>
+          <t>Collections engine, all debt schedules, ending cash, UNFUNDED NEED</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Case matrix:</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Downside</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Upside</t>
+      <c r="B34" s="48" t="inlineStr">
+        <is>
+          <t>Balance Sheet</t>
+        </is>
+      </c>
+      <c r="D34" s="49" t="inlineStr">
+        <is>
+          <t>No-plug balance sheet; check row = 0 in every month</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Census capture</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="8" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>1.1</v>
+      <c r="B35" s="48" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="D35" s="49" t="inlineStr">
+        <is>
+          <t>Integrity tests + viability metrics; master check</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Payroll adjustment</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>0</v>
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D36" s="49" t="inlineStr">
+        <is>
+          <t>KPIs a lender reads first: DSCR, DSO, cap cushion, margins</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CHOW hold (months)</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>0</v>
+      <c r="B37" s="48" t="inlineStr">
+        <is>
+          <t>3-Year Summary</t>
+        </is>
+      </c>
+      <c r="D37" s="49" t="inlineStr">
+        <is>
+          <t>Annual rollup and global DSCR</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE census capture (formula)</t>
-        </is>
-      </c>
-      <c r="B38" s="11">
-        <f>CHOOSE('Control Tower'!$B$33,'Control Tower'!$B$35,'Control Tower'!$C$35,'Control Tower'!$D$35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE payroll adjustment (formula)</t>
-        </is>
-      </c>
-      <c r="B39" s="11">
-        <f>CHOOSE('Control Tower'!$B$33,'Control Tower'!$B$36,'Control Tower'!$C$36,'Control Tower'!$D$36)</f>
-        <v/>
+      <c r="B38" s="48" t="inlineStr">
+        <is>
+          <t>Actuals vs Budget</t>
+        </is>
+      </c>
+      <c r="D38" s="49" t="inlineStr">
+        <is>
+          <t>Enter actuals monthly; variances compute</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE CHOW hold (formula)</t>
-        </is>
-      </c>
-      <c r="B40" s="12">
-        <f>CHOOSE('Control Tower'!$B$33,'Control Tower'!$B$37,'Control Tower'!$C$37,'Control Tower'!$D$37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>REVENUE - CMS FY2026 SMITH COUNTY  (Acct 3000/3010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Medicare RHC HIGH rate, days 1-60 ($/day, net of seq.)</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="n">
-        <v>212.76</v>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>217.10 x 98 pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Medicare RHC LOW rate, days 61+ ($/day, net of seq.)</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="n">
-        <v>167.7</v>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>171.12 x 98 pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Texas Medicaid rate ($/day)</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="n">
-        <v>155</v>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>verify with TMHP</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Medicare payer mix</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>% Medicare days at HIGH rate</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>transfer panel mostly days 61+</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Billing company fee (% of gross, Acct 6510-Z)</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>CMS rate escalation (annual, yrs 2-3)</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Opex inflation on fixed G&amp;A/facility (annual, yrs 2-3)</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>COLLECTIONS TIMING  (cash engine)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>% collected same month</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>% collected month +1</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>% collected month +2</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>CLINICAL LABOR  (Acct 4000; benefits/WC per audit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Benefits &amp; payroll tax load (employed)</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>post-audit: bottom of 22-28% band</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Workers comp (% of employed payroll)</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Salary escalation (annual, yrs 2-3)</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>RN Case Manager salary</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>RN caseload (patients : 1 FTE)</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>RN On-Call salary (per 1.0 FTE)</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>RN On-Call minimum FTE</t>
-        </is>
-      </c>
-      <c r="B61" s="14" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Hospice Aide / CNA salary</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>CNA caseload (patients : 1 FTE)</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>MSW salary</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="n">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>MSW caseload (patients : 1 FTE)</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>Chaplain base PRN contract ($/mo, Acct 4020-0-6-7)</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>Medical director stipend ($/mo, Acct 4020-0-6-M)</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>Medical director start month</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>PRN PER-VISIT SUPPLEMENT  (1099; fires when FTE capacity &lt; required visits)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>RN required visits / patient / month</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>CoP 418.56 - q14 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>RN visits capacity / FTE / month</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>RN PRN rate ($/visit)</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>Aide required visits / patient / month</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>Aide visits capacity / FTE / month</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>Aide PRN rate ($/visit)</t>
-        </is>
-      </c>
-      <c r="B75" s="13" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>MSW required visits / patient / month</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>MSW visits capacity / FTE / month</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>MSW PRN rate ($/visit)</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>Chaplain required visits / patient / month</t>
-        </is>
-      </c>
-      <c r="B79" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>Chaplain visits covered by base contract</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>Chaplain PRN rate ($/visit)</t>
-        </is>
-      </c>
-      <c r="B81" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>INDIRECT LABOR - ADMIN &amp; LEADERSHIP  (Acct 4000-0-*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>Silas Shelton - Executive Director salary</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="n">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  start month</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>Dana Davenport - Director of Nursing salary</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="n">
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  start month</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>Brad Woodard - Director of Sales salary</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="n">
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  start month</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>Rhonda Smith - ADON / Intake salary</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="n">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  start month</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>Volunteer + Bereavement Coordinator salary</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="n">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  start month</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>QAPI / Compliance salary (per 1.0 FTE)</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="n">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>QAPI 0.5 FTE fires at ADC &gt;=</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>DIRECT PATIENT CARE - per patient-day  (Acct 5050-5120)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>DME rental ($/PD, 5050)</t>
-        </is>
-      </c>
-      <c r="B96" s="13" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>Medications ($/PD, 5100)</t>
-        </is>
-      </c>
-      <c r="B97" s="13" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>Medical supplies ($/PD, 5090)</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>Clinical mileage ($/PD, 5110)</t>
-        </is>
-      </c>
-      <c r="B99" s="13" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>Mobile communications - clinical ($/mo, 5120)</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>FACILITY  (700 N Main St - Acct 6010-6150; rent steps with census)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>Rent - Year 1 ($/mo)</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>Rent - Year 2 ($/mo)</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>Rent - Year 3 ($/mo)</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="n">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>Utilities ($/mo, 6150)</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance &amp; repairs ($/mo, 6060)</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>Alarm system ($/mo, 6010)</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>G&amp;A  (MAX(fixed, % of net revenue) per audit pattern)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>EMR base platform ($/mo)</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>EMR per active patient ($/patient/mo)</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>Malpractice / professional liability  (6580-Z)</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="n">
-        <v>833.33</v>
-      </c>
-      <c r="C111" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t>General liability insurance  (6580-Z)</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="C112" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>Phone &amp; internet  (6710-Z)</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="C113" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>Marketing &amp; referral development  (6800-M)</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C114" s="15" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>Accounting &amp; bookkeeping  (6510-Z)</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="n">
-        <v>950</v>
-      </c>
-      <c r="C115" s="15" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>Legal &amp; compliance  (6600-Z)</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="C116" s="15" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>starts month 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>Office supplies  (6650-Z)</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="C117" s="15" t="n">
-        <v>0.005</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>Continuing education &amp; licensing  (6560-Z)</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="C118" s="15" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>Dues &amp; subscriptions  (6570/6705)</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="C119" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>Postage, printing &amp; copier  (6565/6670)</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="C120" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>Contingency reserve (below EBITDA - non-GAAP buffer)  (6640-Z)</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="C121" s="15" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>REAL-CASH DISCIPLINE (no revolver / no invented capital - shortfalls are SHOWN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>OWNER-DEFERRAL TOGGLE (1 = Silas/Dana/Brad defer to break-even)</t>
-        </is>
-      </c>
-      <c r="B123" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>wages accrue on P&amp;L; cash paid once prior-month ADC &gt;= threshold; accrual repaid at repay month</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>Deferral release: prior-month ADC threshold</t>
-        </is>
-      </c>
-      <c r="B124" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>~break-even census</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>Deferred-comp repayment month</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>7 = January (post-collections catch-up)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>CLINICAL HIRE LAG (1 = staff to prior-month census)</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>PRN 1099 supplement covers the gap at per-visit rates</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>Day-1 core RN FTE (floor)</t>
-        </is>
-      </c>
-      <c r="B127" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>Day-1 core CNA FTE (floor)</t>
-        </is>
-      </c>
-      <c r="B128" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>SELLER-DEFERRAL CONTINGENCY (1 = installments roll to Jan balloon)</t>
-        </is>
-      </c>
-      <c r="B129" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>documented fallback - NOT base</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>Investor notes raised (10% IO qtrly, 3-yr) - REAL ONLY</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>0 = none assumed; set only when checks clear</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>Investor notes landing month</t>
-        </is>
-      </c>
-      <c r="B131" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>Investor note rate (APR, interest-only quarterly)</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>Cash warning threshold (reporting/formatting only)</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>no facility behind it - display only</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>TX franchise/margin tax (% of NPR if profitable)</t>
-        </is>
-      </c>
-      <c r="B134" s="15" t="n">
-        <v>0.00375</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>Medicare aggregate cap / beneficiary (FY2026)</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="n">
-        <v>33900</v>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>monitor on Medicare CAP logic</t>
+      <c r="B40" s="50" t="inlineStr">
+        <is>
+          <t>Confidential - prepared for lender and investor diligence. Figures QA-verified by automated test harness (23 checks).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A122:D122"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A82:D82"/>
-    <mergeCell ref="A95:D95"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A108:D108"/>
-    <mergeCell ref="A1:N1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AL14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="4" max="4"/>
+    <col width="10.5" customWidth="1" min="5" max="5"/>
+    <col width="10.5" customWidth="1" min="6" max="6"/>
+    <col width="10.5" customWidth="1" min="7" max="7"/>
+    <col width="10.5" customWidth="1" min="8" max="8"/>
+    <col width="10.5" customWidth="1" min="9" max="9"/>
+    <col width="10.5" customWidth="1" min="10" max="10"/>
+    <col width="10.5" customWidth="1" min="11" max="11"/>
+    <col width="10.5" customWidth="1" min="12" max="12"/>
+    <col width="10.5" customWidth="1" min="13" max="13"/>
+    <col width="10.5" customWidth="1" min="14" max="14"/>
+    <col width="10.5" customWidth="1" min="15" max="15"/>
+    <col width="10.5" customWidth="1" min="16" max="16"/>
+    <col width="10.5" customWidth="1" min="17" max="17"/>
+    <col width="10.5" customWidth="1" min="18" max="18"/>
+    <col width="10.5" customWidth="1" min="19" max="19"/>
+    <col width="10.5" customWidth="1" min="20" max="20"/>
+    <col width="10.5" customWidth="1" min="21" max="21"/>
+    <col width="10.5" customWidth="1" min="22" max="22"/>
+    <col width="10.5" customWidth="1" min="23" max="23"/>
+    <col width="10.5" customWidth="1" min="24" max="24"/>
+    <col width="10.5" customWidth="1" min="25" max="25"/>
+    <col width="10.5" customWidth="1" min="26" max="26"/>
+    <col width="10.5" customWidth="1" min="27" max="27"/>
+    <col width="10.5" customWidth="1" min="28" max="28"/>
+    <col width="10.5" customWidth="1" min="29" max="29"/>
+    <col width="10.5" customWidth="1" min="30" max="30"/>
+    <col width="10.5" customWidth="1" min="31" max="31"/>
+    <col width="10.5" customWidth="1" min="32" max="32"/>
+    <col width="10.5" customWidth="1" min="33" max="33"/>
+    <col width="10.5" customWidth="1" min="34" max="34"/>
+    <col width="10.5" customWidth="1" min="35" max="35"/>
+    <col width="10.5" customWidth="1" min="36" max="36"/>
+    <col width="10.5" customWidth="1" min="37" max="37"/>
+    <col width="10.5" customWidth="1" min="38" max="38"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AZALEA HOSPICE - REFUGE OPERATING MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CHECKS - every integrity test in one place. MASTER must read 0 / OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Month #</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="O4" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="P4" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="R4" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="S4" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T4" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="U4" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="V4" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="W4" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="X4" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y4" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z4" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA4" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB4" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC4" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD4" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE4" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF4" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG4" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH4" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI4" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ4" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK4" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL4" s="16" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr"/>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>Oct-26</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>Nov-26</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>Dec-26</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Jan-27</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>Feb-27</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>Mar-27</t>
+        </is>
+      </c>
+      <c r="L5" s="17" t="inlineStr">
+        <is>
+          <t>Apr-27</t>
+        </is>
+      </c>
+      <c r="M5" s="17" t="inlineStr">
+        <is>
+          <t>May-27</t>
+        </is>
+      </c>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t>Jun-27</t>
+        </is>
+      </c>
+      <c r="O5" s="17" t="inlineStr">
+        <is>
+          <t>Jul-27</t>
+        </is>
+      </c>
+      <c r="P5" s="17" t="inlineStr">
+        <is>
+          <t>Aug-27</t>
+        </is>
+      </c>
+      <c r="Q5" s="17" t="inlineStr">
+        <is>
+          <t>Sep-27</t>
+        </is>
+      </c>
+      <c r="R5" s="17" t="inlineStr">
+        <is>
+          <t>Oct-27</t>
+        </is>
+      </c>
+      <c r="S5" s="17" t="inlineStr">
+        <is>
+          <t>Nov-27</t>
+        </is>
+      </c>
+      <c r="T5" s="17" t="inlineStr">
+        <is>
+          <t>Dec-27</t>
+        </is>
+      </c>
+      <c r="U5" s="17" t="inlineStr">
+        <is>
+          <t>Jan-28</t>
+        </is>
+      </c>
+      <c r="V5" s="17" t="inlineStr">
+        <is>
+          <t>Feb-28</t>
+        </is>
+      </c>
+      <c r="W5" s="17" t="inlineStr">
+        <is>
+          <t>Mar-28</t>
+        </is>
+      </c>
+      <c r="X5" s="17" t="inlineStr">
+        <is>
+          <t>Apr-28</t>
+        </is>
+      </c>
+      <c r="Y5" s="17" t="inlineStr">
+        <is>
+          <t>May-28</t>
+        </is>
+      </c>
+      <c r="Z5" s="17" t="inlineStr">
+        <is>
+          <t>Jun-28</t>
+        </is>
+      </c>
+      <c r="AA5" s="17" t="inlineStr">
+        <is>
+          <t>Jul-28</t>
+        </is>
+      </c>
+      <c r="AB5" s="17" t="inlineStr">
+        <is>
+          <t>Aug-28</t>
+        </is>
+      </c>
+      <c r="AC5" s="17" t="inlineStr">
+        <is>
+          <t>Sep-28</t>
+        </is>
+      </c>
+      <c r="AD5" s="17" t="inlineStr">
+        <is>
+          <t>Oct-28</t>
+        </is>
+      </c>
+      <c r="AE5" s="17" t="inlineStr">
+        <is>
+          <t>Nov-28</t>
+        </is>
+      </c>
+      <c r="AF5" s="17" t="inlineStr">
+        <is>
+          <t>Dec-28</t>
+        </is>
+      </c>
+      <c r="AG5" s="17" t="inlineStr">
+        <is>
+          <t>Jan-29</t>
+        </is>
+      </c>
+      <c r="AH5" s="17" t="inlineStr">
+        <is>
+          <t>Feb-29</t>
+        </is>
+      </c>
+      <c r="AI5" s="17" t="inlineStr">
+        <is>
+          <t>Mar-29</t>
+        </is>
+      </c>
+      <c r="AJ5" s="17" t="inlineStr">
+        <is>
+          <t>Apr-29</t>
+        </is>
+      </c>
+      <c r="AK5" s="17" t="inlineStr">
+        <is>
+          <t>May-29</t>
+        </is>
+      </c>
+      <c r="AL5" s="17" t="inlineStr">
+        <is>
+          <t>Jun-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>BS out of balance (abs &gt; $0.01 -&gt; 1)</t>
+        </is>
+      </c>
+      <c r="C6" s="25">
+        <f>IF(ABS('Balance Sheet'!C22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="25">
+        <f>IF(ABS('Balance Sheet'!D22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="25">
+        <f>IF(ABS('Balance Sheet'!E22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="25">
+        <f>IF(ABS('Balance Sheet'!F22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="25">
+        <f>IF(ABS('Balance Sheet'!G22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="25">
+        <f>IF(ABS('Balance Sheet'!H22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="I6" s="25">
+        <f>IF(ABS('Balance Sheet'!I22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="J6" s="25">
+        <f>IF(ABS('Balance Sheet'!J22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="25">
+        <f>IF(ABS('Balance Sheet'!K22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="L6" s="25">
+        <f>IF(ABS('Balance Sheet'!L22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="M6" s="25">
+        <f>IF(ABS('Balance Sheet'!M22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="N6" s="25">
+        <f>IF(ABS('Balance Sheet'!N22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="O6" s="25">
+        <f>IF(ABS('Balance Sheet'!O22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="P6" s="25">
+        <f>IF(ABS('Balance Sheet'!P22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="Q6" s="25">
+        <f>IF(ABS('Balance Sheet'!Q22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="R6" s="25">
+        <f>IF(ABS('Balance Sheet'!R22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="S6" s="25">
+        <f>IF(ABS('Balance Sheet'!S22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="T6" s="25">
+        <f>IF(ABS('Balance Sheet'!T22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="U6" s="25">
+        <f>IF(ABS('Balance Sheet'!U22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="V6" s="25">
+        <f>IF(ABS('Balance Sheet'!V22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="W6" s="25">
+        <f>IF(ABS('Balance Sheet'!W22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="X6" s="25">
+        <f>IF(ABS('Balance Sheet'!X22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="Y6" s="25">
+        <f>IF(ABS('Balance Sheet'!Y22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="Z6" s="25">
+        <f>IF(ABS('Balance Sheet'!Z22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AA6" s="25">
+        <f>IF(ABS('Balance Sheet'!AA22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AB6" s="25">
+        <f>IF(ABS('Balance Sheet'!AB22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AC6" s="25">
+        <f>IF(ABS('Balance Sheet'!AC22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AD6" s="25">
+        <f>IF(ABS('Balance Sheet'!AD22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AE6" s="25">
+        <f>IF(ABS('Balance Sheet'!AE22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AF6" s="25">
+        <f>IF(ABS('Balance Sheet'!AF22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AG6" s="25">
+        <f>IF(ABS('Balance Sheet'!AG22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AH6" s="25">
+        <f>IF(ABS('Balance Sheet'!AH22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AI6" s="25">
+        <f>IF(ABS('Balance Sheet'!AI22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="25">
+        <f>IF(ABS('Balance Sheet'!AJ22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AK6" s="25">
+        <f>IF(ABS('Balance Sheet'!AK22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AL6" s="25">
+        <f>IF(ABS('Balance Sheet'!AL22)&gt;0.01,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Seller balance negative (-&gt; 1)</t>
+        </is>
+      </c>
+      <c r="C7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!C16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!D16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="E7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!E16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!F16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!G16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!H16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="I7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!I16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="J7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!J16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!K16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="L7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!L16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="M7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!M16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="N7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!N16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="O7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!O16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="P7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!P16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!Q16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="R7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!R16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="S7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!S16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="T7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!T16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="U7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!U16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="V7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!V16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="W7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!W16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="X7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!X16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="Y7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!Y16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="Z7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!Z16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AA7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AA16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AB7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AB16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AC7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AC16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AD7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AD16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AE7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AE16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AF7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AF16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AG7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AG16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AH7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AH16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AI7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AI16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AJ16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AK7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AK16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AL7" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AL16&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Cash below zero (VIABILITY - reported, not integrity)</t>
+        </is>
+      </c>
+      <c r="C8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!C43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!D43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!E43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!F43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!G43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!H43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="I8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!I43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!J43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!K43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!L43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="M8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!M43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="N8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!N43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="O8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!O43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="P8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!P43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!Q43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="R8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!R43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="S8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!S43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="T8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!T43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="U8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!U43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="V8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!V43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="W8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!W43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="X8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!X43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="Y8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!Y43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="Z8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!Z43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AA8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AA43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AB8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AB43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AC8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AC43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AD8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AD43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AE8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AE43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AF8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AF43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AG8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AG43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AH8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AH43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AI8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AI43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AJ43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AK8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AK43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+      <c r="AL8" s="25">
+        <f>IF('Cash Flow &amp; Runway'!AL43&lt;-0.01,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Collections conservation: cum collected + AR - cum NPR (should be 0)</t>
+        </is>
+      </c>
+      <c r="B10" s="23">
+        <f>SUM('Cash Flow &amp; Runway'!C9:AL9)+'Cash Flow &amp; Runway'!AL10-SUM('Cash Flow &amp; Runway'!C8:AL8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Deferral conservation: cum accrued - cum repaid - end balance (should be 0)</t>
+        </is>
+      </c>
+      <c r="B11" s="23">
+        <f>SUM('Staffing'!C42:AL42)-SUM('Staffing'!C43:AL43)-'Staffing'!AL44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>MASTER INTEGRITY CHECK (0 = OK; cash viability reported separately)</t>
+        </is>
+      </c>
+      <c r="B12" s="30">
+        <f>SUM(C6:AL6)+SUM(C7:AL7)+IF(ABS(B10)&gt;1,1,0)+IF(ABS(B11)&gt;1,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>MONTHS WITH CASH BELOW ZERO (viability count)</t>
+        </is>
+      </c>
+      <c r="B13" s="31">
+        <f>SUM(C8:AL8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>PEAK ADDITIONAL CAPITAL REQUIRED</t>
+        </is>
+      </c>
+      <c r="B14" s="24">
+        <f>'Cash Flow &amp; Runway'!B47</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="0000B050"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5607,15 +5407,24 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5789,15 +5598,24 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00538135"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6545,15 +6363,1581 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F3864"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N135"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AZALEA HOSPICE - REFUGE OPERATING MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL TOWER - every number in the model flows from this tab. Yellow = input; everything else is formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>COMPANY &amp; DEAL  (current Refuge structure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Starting capital on deposit (equity)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Jim Bullard $195K + owner $55K</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Pre-opening / startup spend from capital</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0 = funded elsewhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Refuge license purchase price (100% membership CHOW)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Acct 1980 intangible</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Down payment at closing (Month 1)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Seller monthly payment (MIPA 7/14/2026)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>31250</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>$31,250/mo Sep-Dec per executed MIPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>First seller payment month</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>3 = September</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Last seller payment month</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>6 = December</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Seller note simple interest (APR)</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Balloon month (36-month rule / January)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Balloon takeout note rate (APR)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>BASE CASE: SBA/bank funds the Jan balloon; modeled at the conservative 6%/36 basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Balloon takeout note term (months)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BANK-REFI TOGGLE (1 = $500K/6%/36 funds Sept - BASE)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>BASE = 1: Bullard-relationship bank refi (confirmed) pays seller Sept; 0 = seller carried to Jan balloon per MIPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Full-refi funding month</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>3 = September</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Full-refi amount</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Full-refi rate (APR)</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Full-refi term (months)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>SBA TOGGLE (1 = SBA 7(a) funds &amp; REFINANCES the bank note) - BASE</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>SBA proceeds pay off the bank-refi balance at funding month</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>SBA funding month</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>7 = January (51% transfer / 42 CFR 424.550(b) date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>SBA amount</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>SBA rate (APR)</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SBA term (months)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>10-year 7(a); ~$6,747/mo at 10.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>License intangible amortization (yrs, Acct 7200)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>CHOW / go-live month (amortization starts)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>CENSUS  (admissions row lives on Census Waterfall - blue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Days per month (model uniform)</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Average length of stay (days)</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>drives discharges = BOM x days/ALOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Deaths as share of discharges</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>SCENARIO CASES  (1 = Base, 2 = Downside, 3 = Upside; active values are formulas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE CASE</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>flip 1/2/3 - drives capture, payroll adj, CHOW hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Case matrix:</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Census capture</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Payroll adjustment</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CHOW hold (months)</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE census capture (formula)</t>
+        </is>
+      </c>
+      <c r="B38" s="11">
+        <f>CHOOSE('Control Tower'!$B$33,'Control Tower'!$B$35,'Control Tower'!$C$35,'Control Tower'!$D$35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE payroll adjustment (formula)</t>
+        </is>
+      </c>
+      <c r="B39" s="11">
+        <f>CHOOSE('Control Tower'!$B$33,'Control Tower'!$B$36,'Control Tower'!$C$36,'Control Tower'!$D$36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE CHOW hold (formula)</t>
+        </is>
+      </c>
+      <c r="B40" s="12">
+        <f>CHOOSE('Control Tower'!$B$33,'Control Tower'!$B$37,'Control Tower'!$C$37,'Control Tower'!$D$37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>REVENUE - CMS FY2026 SMITH COUNTY  (Acct 3000/3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Medicare RHC HIGH rate, days 1-60 ($/day, net of seq.)</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
+        <v>212.76</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>217.10 x 98 pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Medicare RHC LOW rate, days 61+ ($/day, net of seq.)</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="n">
+        <v>167.7</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>171.12 x 98 pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Texas Medicaid rate ($/day)</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="n">
+        <v>155</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>verify with TMHP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Medicare payer mix</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>% Medicare days at HIGH rate</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>transfer panel mostly days 61+</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Billing company fee (% of gross, Acct 6510-Z)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>CMS rate escalation (annual, yrs 2-3)</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Opex inflation on fixed G&amp;A/facility (annual, yrs 2-3)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>COLLECTIONS TIMING  (cash engine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>% collected same month</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>% collected month +1</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>% collected month +2</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>CLINICAL LABOR  (Acct 4000; benefits/WC per audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Benefits &amp; payroll tax load (employed)</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>post-audit: bottom of 22-28% band</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Workers comp (% of employed payroll)</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Salary escalation (annual, yrs 2-3)</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>RN Case Manager salary</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>RN caseload (patients : 1 FTE)</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>RN On-Call salary (per 1.0 FTE)</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>RN On-Call minimum FTE</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Hospice Aide / CNA salary</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>CNA caseload (patients : 1 FTE)</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>MSW salary</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>MSW caseload (patients : 1 FTE)</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Chaplain base PRN contract ($/mo, Acct 4020-0-6-7)</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Medical director stipend ($/mo, Acct 4020-0-6-M)</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Medical director start month</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>PRN PER-VISIT SUPPLEMENT  (1099; fires when FTE capacity &lt; required visits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>RN required visits / patient / month</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>CoP 418.56 - q14 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>RN visits capacity / FTE / month</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>RN PRN rate ($/visit)</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Aide required visits / patient / month</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Aide visits capacity / FTE / month</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Aide PRN rate ($/visit)</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>MSW required visits / patient / month</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>MSW visits capacity / FTE / month</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>MSW PRN rate ($/visit)</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Chaplain required visits / patient / month</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Chaplain visits covered by base contract</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Chaplain PRN rate ($/visit)</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>INDIRECT LABOR - ADMIN &amp; LEADERSHIP  (Acct 4000-0-*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Silas Shelton - Executive Director salary</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  start month</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Dana Davenport - Director of Nursing salary</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  start month</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Brad Woodard - Director of Sales salary</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  start month</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Rhonda Smith - ADON / Intake salary</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  start month</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer + Bereavement Coordinator salary</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  start month</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>QAPI / Compliance salary (per 1.0 FTE)</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>QAPI 0.5 FTE fires at ADC &gt;=</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>DIRECT PATIENT CARE - per patient-day  (Acct 5050-5120)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>DME rental ($/PD, 5050)</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>Medications ($/PD, 5100)</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Medical supplies ($/PD, 5090)</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Clinical mileage ($/PD, 5110)</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Mobile communications - clinical ($/mo, 5120)</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>FACILITY  (700 N Main St - Acct 6010-6150; rent steps with census)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Rent - Year 1 ($/mo)</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Rent - Year 2 ($/mo)</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Rent - Year 3 ($/mo)</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Utilities ($/mo, 6150)</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance &amp; repairs ($/mo, 6060)</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Alarm system ($/mo, 6010)</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>G&amp;A  (MAX(fixed, % of net revenue) per audit pattern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>EMR base platform ($/mo)</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>EMR per active patient ($/patient/mo)</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Malpractice / professional liability  (6580-Z)</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>833.33</v>
+      </c>
+      <c r="C111" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>General liability insurance  (6580-Z)</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C112" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Phone &amp; internet  (6710-Z)</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C113" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Marketing &amp; referral development  (6800-M)</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C114" s="15" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Accounting &amp; bookkeeping  (6510-Z)</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>950</v>
+      </c>
+      <c r="C115" s="15" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>Legal &amp; compliance  (6600-Z)</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C116" s="15" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>starts month 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Office supplies  (6650-Z)</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C117" s="15" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>Continuing education &amp; licensing  (6560-Z)</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C118" s="15" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>Dues &amp; subscriptions  (6570/6705)</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C119" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>Postage, printing &amp; copier  (6565/6670)</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="C120" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Contingency reserve (below EBITDA - non-GAAP buffer)  (6640-Z)</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C121" s="15" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>REAL-CASH DISCIPLINE (no revolver / no invented capital - shortfalls are SHOWN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>OWNER-DEFERRAL TOGGLE (1 = Silas/Dana/Brad defer to break-even)</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>wages accrue on P&amp;L; cash paid once prior-month ADC &gt;= threshold; accrual repaid at repay month</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>Deferral release: prior-month ADC threshold</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>~break-even census</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>Deferred-comp repayment month</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>7 = January (post-collections catch-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>CLINICAL HIRE LAG (1 = staff to prior-month census)</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>PRN 1099 supplement covers the gap at per-visit rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>Day-1 core RN FTE (floor)</t>
+        </is>
+      </c>
+      <c r="B127" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>Day-1 core CNA FTE (floor)</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>SELLER-DEFERRAL CONTINGENCY (1 = installments roll to Jan balloon)</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>documented fallback - NOT base</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>Investor notes raised (10% IO qtrly, 3-yr) - REAL ONLY</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>0 = none assumed; set only when checks clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Investor notes landing month</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>Investor note rate (APR, interest-only quarterly)</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>Cash warning threshold (reporting/formatting only)</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>no facility behind it - display only</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>TX franchise/margin tax (% of NPR if profitable)</t>
+        </is>
+      </c>
+      <c r="B134" s="15" t="n">
+        <v>0.00375</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>Medicare aggregate cap / beneficiary (FY2026)</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>monitor on Medicare CAP logic</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A108:D108"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="002E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8088,15 +9472,24 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -9365,15 +10758,24 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -14910,15 +16312,24 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -18929,15 +20340,24 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -22042,15 +23462,24 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -27482,15 +28911,24 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -30420,884 +31858,14 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00FF0000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AL14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="10.5" customWidth="1" min="3" max="3"/>
-    <col width="10.5" customWidth="1" min="4" max="4"/>
-    <col width="10.5" customWidth="1" min="5" max="5"/>
-    <col width="10.5" customWidth="1" min="6" max="6"/>
-    <col width="10.5" customWidth="1" min="7" max="7"/>
-    <col width="10.5" customWidth="1" min="8" max="8"/>
-    <col width="10.5" customWidth="1" min="9" max="9"/>
-    <col width="10.5" customWidth="1" min="10" max="10"/>
-    <col width="10.5" customWidth="1" min="11" max="11"/>
-    <col width="10.5" customWidth="1" min="12" max="12"/>
-    <col width="10.5" customWidth="1" min="13" max="13"/>
-    <col width="10.5" customWidth="1" min="14" max="14"/>
-    <col width="10.5" customWidth="1" min="15" max="15"/>
-    <col width="10.5" customWidth="1" min="16" max="16"/>
-    <col width="10.5" customWidth="1" min="17" max="17"/>
-    <col width="10.5" customWidth="1" min="18" max="18"/>
-    <col width="10.5" customWidth="1" min="19" max="19"/>
-    <col width="10.5" customWidth="1" min="20" max="20"/>
-    <col width="10.5" customWidth="1" min="21" max="21"/>
-    <col width="10.5" customWidth="1" min="22" max="22"/>
-    <col width="10.5" customWidth="1" min="23" max="23"/>
-    <col width="10.5" customWidth="1" min="24" max="24"/>
-    <col width="10.5" customWidth="1" min="25" max="25"/>
-    <col width="10.5" customWidth="1" min="26" max="26"/>
-    <col width="10.5" customWidth="1" min="27" max="27"/>
-    <col width="10.5" customWidth="1" min="28" max="28"/>
-    <col width="10.5" customWidth="1" min="29" max="29"/>
-    <col width="10.5" customWidth="1" min="30" max="30"/>
-    <col width="10.5" customWidth="1" min="31" max="31"/>
-    <col width="10.5" customWidth="1" min="32" max="32"/>
-    <col width="10.5" customWidth="1" min="33" max="33"/>
-    <col width="10.5" customWidth="1" min="34" max="34"/>
-    <col width="10.5" customWidth="1" min="35" max="35"/>
-    <col width="10.5" customWidth="1" min="36" max="36"/>
-    <col width="10.5" customWidth="1" min="37" max="37"/>
-    <col width="10.5" customWidth="1" min="38" max="38"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AZALEA HOSPICE - REFUGE OPERATING MODEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CHECKS - every integrity test in one place. MASTER must read 0 / OK.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Month #</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="J4" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="L4" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="N4" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="O4" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="P4" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q4" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="R4" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="S4" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="T4" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="U4" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="V4" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="W4" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="X4" s="16" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y4" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z4" s="16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA4" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB4" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC4" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AD4" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE4" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF4" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG4" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="AH4" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI4" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="AJ4" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK4" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="AL4" s="16" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr"/>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Aug-26</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>Sep-26</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>Oct-26</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>Nov-26</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>Dec-26</t>
-        </is>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>Jan-27</t>
-        </is>
-      </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t>Feb-27</t>
-        </is>
-      </c>
-      <c r="K5" s="17" t="inlineStr">
-        <is>
-          <t>Mar-27</t>
-        </is>
-      </c>
-      <c r="L5" s="17" t="inlineStr">
-        <is>
-          <t>Apr-27</t>
-        </is>
-      </c>
-      <c r="M5" s="17" t="inlineStr">
-        <is>
-          <t>May-27</t>
-        </is>
-      </c>
-      <c r="N5" s="17" t="inlineStr">
-        <is>
-          <t>Jun-27</t>
-        </is>
-      </c>
-      <c r="O5" s="17" t="inlineStr">
-        <is>
-          <t>Jul-27</t>
-        </is>
-      </c>
-      <c r="P5" s="17" t="inlineStr">
-        <is>
-          <t>Aug-27</t>
-        </is>
-      </c>
-      <c r="Q5" s="17" t="inlineStr">
-        <is>
-          <t>Sep-27</t>
-        </is>
-      </c>
-      <c r="R5" s="17" t="inlineStr">
-        <is>
-          <t>Oct-27</t>
-        </is>
-      </c>
-      <c r="S5" s="17" t="inlineStr">
-        <is>
-          <t>Nov-27</t>
-        </is>
-      </c>
-      <c r="T5" s="17" t="inlineStr">
-        <is>
-          <t>Dec-27</t>
-        </is>
-      </c>
-      <c r="U5" s="17" t="inlineStr">
-        <is>
-          <t>Jan-28</t>
-        </is>
-      </c>
-      <c r="V5" s="17" t="inlineStr">
-        <is>
-          <t>Feb-28</t>
-        </is>
-      </c>
-      <c r="W5" s="17" t="inlineStr">
-        <is>
-          <t>Mar-28</t>
-        </is>
-      </c>
-      <c r="X5" s="17" t="inlineStr">
-        <is>
-          <t>Apr-28</t>
-        </is>
-      </c>
-      <c r="Y5" s="17" t="inlineStr">
-        <is>
-          <t>May-28</t>
-        </is>
-      </c>
-      <c r="Z5" s="17" t="inlineStr">
-        <is>
-          <t>Jun-28</t>
-        </is>
-      </c>
-      <c r="AA5" s="17" t="inlineStr">
-        <is>
-          <t>Jul-28</t>
-        </is>
-      </c>
-      <c r="AB5" s="17" t="inlineStr">
-        <is>
-          <t>Aug-28</t>
-        </is>
-      </c>
-      <c r="AC5" s="17" t="inlineStr">
-        <is>
-          <t>Sep-28</t>
-        </is>
-      </c>
-      <c r="AD5" s="17" t="inlineStr">
-        <is>
-          <t>Oct-28</t>
-        </is>
-      </c>
-      <c r="AE5" s="17" t="inlineStr">
-        <is>
-          <t>Nov-28</t>
-        </is>
-      </c>
-      <c r="AF5" s="17" t="inlineStr">
-        <is>
-          <t>Dec-28</t>
-        </is>
-      </c>
-      <c r="AG5" s="17" t="inlineStr">
-        <is>
-          <t>Jan-29</t>
-        </is>
-      </c>
-      <c r="AH5" s="17" t="inlineStr">
-        <is>
-          <t>Feb-29</t>
-        </is>
-      </c>
-      <c r="AI5" s="17" t="inlineStr">
-        <is>
-          <t>Mar-29</t>
-        </is>
-      </c>
-      <c r="AJ5" s="17" t="inlineStr">
-        <is>
-          <t>Apr-29</t>
-        </is>
-      </c>
-      <c r="AK5" s="17" t="inlineStr">
-        <is>
-          <t>May-29</t>
-        </is>
-      </c>
-      <c r="AL5" s="17" t="inlineStr">
-        <is>
-          <t>Jun-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>BS out of balance (abs &gt; $0.01 -&gt; 1)</t>
-        </is>
-      </c>
-      <c r="C6" s="25">
-        <f>IF(ABS('Balance Sheet'!C22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="25">
-        <f>IF(ABS('Balance Sheet'!D22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="E6" s="25">
-        <f>IF(ABS('Balance Sheet'!E22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="25">
-        <f>IF(ABS('Balance Sheet'!F22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="25">
-        <f>IF(ABS('Balance Sheet'!G22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="H6" s="25">
-        <f>IF(ABS('Balance Sheet'!H22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="I6" s="25">
-        <f>IF(ABS('Balance Sheet'!I22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="J6" s="25">
-        <f>IF(ABS('Balance Sheet'!J22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="K6" s="25">
-        <f>IF(ABS('Balance Sheet'!K22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="L6" s="25">
-        <f>IF(ABS('Balance Sheet'!L22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="M6" s="25">
-        <f>IF(ABS('Balance Sheet'!M22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="N6" s="25">
-        <f>IF(ABS('Balance Sheet'!N22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="O6" s="25">
-        <f>IF(ABS('Balance Sheet'!O22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="P6" s="25">
-        <f>IF(ABS('Balance Sheet'!P22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="25">
-        <f>IF(ABS('Balance Sheet'!Q22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="R6" s="25">
-        <f>IF(ABS('Balance Sheet'!R22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="S6" s="25">
-        <f>IF(ABS('Balance Sheet'!S22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="T6" s="25">
-        <f>IF(ABS('Balance Sheet'!T22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="U6" s="25">
-        <f>IF(ABS('Balance Sheet'!U22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="V6" s="25">
-        <f>IF(ABS('Balance Sheet'!V22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="W6" s="25">
-        <f>IF(ABS('Balance Sheet'!W22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="X6" s="25">
-        <f>IF(ABS('Balance Sheet'!X22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="Y6" s="25">
-        <f>IF(ABS('Balance Sheet'!Y22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="Z6" s="25">
-        <f>IF(ABS('Balance Sheet'!Z22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AA6" s="25">
-        <f>IF(ABS('Balance Sheet'!AA22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AB6" s="25">
-        <f>IF(ABS('Balance Sheet'!AB22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AC6" s="25">
-        <f>IF(ABS('Balance Sheet'!AC22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AD6" s="25">
-        <f>IF(ABS('Balance Sheet'!AD22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AE6" s="25">
-        <f>IF(ABS('Balance Sheet'!AE22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AF6" s="25">
-        <f>IF(ABS('Balance Sheet'!AF22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AG6" s="25">
-        <f>IF(ABS('Balance Sheet'!AG22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AH6" s="25">
-        <f>IF(ABS('Balance Sheet'!AH22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AI6" s="25">
-        <f>IF(ABS('Balance Sheet'!AI22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AJ6" s="25">
-        <f>IF(ABS('Balance Sheet'!AJ22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AK6" s="25">
-        <f>IF(ABS('Balance Sheet'!AK22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AL6" s="25">
-        <f>IF(ABS('Balance Sheet'!AL22)&gt;0.01,1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Seller balance negative (-&gt; 1)</t>
-        </is>
-      </c>
-      <c r="C7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!C16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!D16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="E7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!E16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!F16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!G16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="H7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!H16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="I7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!I16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="J7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!J16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="K7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!K16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="L7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!L16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="M7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!M16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="N7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!N16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="O7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!O16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="P7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!P16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!Q16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="R7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!R16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="S7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!S16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="T7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!T16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="U7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!U16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="V7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!V16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="W7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!W16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="X7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!X16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!Y16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="Z7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!Z16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AA7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AA16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AB7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AB16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AC7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AC16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AD7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AD16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AE7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AE16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AF7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AF16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AG7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AG16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AH7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AH16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AI7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AI16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AJ7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AJ16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AK7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AK16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AL7" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AL16&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Cash below zero (VIABILITY - reported, not integrity)</t>
-        </is>
-      </c>
-      <c r="C8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!C43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!D43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="E8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!E43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!F43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!G43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="H8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!H43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="I8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!I43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!J43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="K8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!K43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="L8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!L43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="M8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!M43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="N8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!N43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="O8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!O43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="P8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!P43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!Q43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="R8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!R43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="S8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!S43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="T8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!T43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="U8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!U43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="V8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!V43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="W8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!W43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="X8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!X43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!Y43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="Z8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!Z43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AA8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AA43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AB8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AB43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AC8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AC43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AD8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AD43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AE8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AE43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AF8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AF43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AG8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AG43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AH8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AH43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AI8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AI43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AJ43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AK8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AK43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-      <c r="AL8" s="25">
-        <f>IF('Cash Flow &amp; Runway'!AL43&lt;-0.01,1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Collections conservation: cum collected + AR - cum NPR (should be 0)</t>
-        </is>
-      </c>
-      <c r="B10" s="23">
-        <f>SUM('Cash Flow &amp; Runway'!C9:AL9)+'Cash Flow &amp; Runway'!AL10-SUM('Cash Flow &amp; Runway'!C8:AL8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Deferral conservation: cum accrued - cum repaid - end balance (should be 0)</t>
-        </is>
-      </c>
-      <c r="B11" s="23">
-        <f>SUM('Staffing'!C42:AL42)-SUM('Staffing'!C43:AL43)-'Staffing'!AL44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>MASTER INTEGRITY CHECK (0 = OK; cash viability reported separately)</t>
-        </is>
-      </c>
-      <c r="B12" s="30">
-        <f>SUM(C6:AL6)+SUM(C7:AL7)+IF(ABS(B10)&gt;1,1,0)+IF(ABS(B11)&gt;1,1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>MONTHS WITH CASH BELOW ZERO (viability count)</t>
-        </is>
-      </c>
-      <c r="B13" s="31">
-        <f>SUM(C8:AL8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>PEAK ADDITIONAL CAPITAL REQUIRED</t>
-        </is>
-      </c>
-      <c r="B14" s="24">
-        <f>'Cash Flow &amp; Runway'!B47</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Azalea Hospice - Proforma Rev 4.10&amp;C&amp;8 Confidential&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/financial_models/output/Azalea_Hospice_Proforma_Rev4.10_DYNAMIC.xlsx
+++ b/financial_models/output/Azalea_Hospice_Proforma_Rev4.10_DYNAMIC.xlsx
@@ -773,14 +773,14 @@
     <row r="8">
       <c r="B8" s="41" t="inlineStr">
         <is>
-          <t>REAL-CASH DISCIPLINE: no revolver or assumed facility anywhere in this model. Cash shortfalls, if any, are shown</t>
+          <t>Working-capital policy: the model assumes no revolving credit facility. Any cash shortfall is presented</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="41" t="inlineStr">
         <is>
-          <t>as UNFUNDED NEED - the amount of additional capital required - never plugged by a balancing facility.</t>
+          <t>explicitly as an additional funding requirement rather than absorbed by an assumed facility.</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
     <row r="15">
       <c r="B15" s="44" t="inlineStr">
         <is>
-          <t>Peak additional capital required (base case)</t>
+          <t>Peak additional funding requirement (base case)</t>
         </is>
       </c>
       <c r="C15" s="45">
@@ -899,7 +899,7 @@
     <row r="22">
       <c r="B22" s="47" t="inlineStr">
         <is>
-          <t>Oct-Dec  - Bank note service $15,211/month; owner salaries deferred until break-even census (accrued, repaid Jan)</t>
+          <t>Oct-Dec  - Bank note service of $15,211/month; management salary deferral until break-even census (repaid January)</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="D27" s="49" t="inlineStr">
         <is>
-          <t>Every model input - deal terms, census, rates, staffing, toggles (scenario, refi, SBA, deferral)</t>
+          <t>All model inputs - deal terms, census, rates, staffing, and scenario settings</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="D30" s="49" t="inlineStr">
         <is>
-          <t>FTEs (census-driven with 1-month hire lag), payroll, PRN supplement, owner-deferral schedule</t>
+          <t>FTEs (census-driven with staged hiring), payroll, PRN supplement, management salary deferral schedule</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="D33" s="49" t="inlineStr">
         <is>
-          <t>Collections engine, all debt schedules, ending cash, UNFUNDED NEED</t>
+          <t>Collections timing, all debt schedules, ending cash, funding requirement (if any)</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D34" s="49" t="inlineStr">
         <is>
-          <t>No-plug balance sheet; check row = 0 in every month</t>
+          <t>Fully articulated balance sheet; check row equals zero in every month</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="D35" s="49" t="inlineStr">
         <is>
-          <t>Integrity tests + viability metrics; master check</t>
+          <t>Model integrity tests and funding-requirement metrics</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D36" s="49" t="inlineStr">
         <is>
-          <t>KPIs a lender reads first: DSCR, DSO, cap cushion, margins</t>
+          <t>Key indicators: DSCR, DSO, Medicare cap cushion, margins</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
     <row r="40">
       <c r="B40" s="50" t="inlineStr">
         <is>
-          <t>Confidential - prepared for lender and investor diligence. Figures QA-verified by automated test harness (23 checks).</t>
+          <t>Confidential - prepared for lender and investor diligence. All figures verified by an automated 23-point test harness.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CHECKS - every integrity test in one place. MASTER must read 0 / OK.</t>
+          <t>CHECKS - model integrity tests. The master check reads 0 when all tests pass.</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Cash below zero (VIABILITY - reported, not integrity)</t>
+          <t>Months with cash below zero (funding-requirement indicator)</t>
         </is>
       </c>
       <c r="C8" s="25">
@@ -1930,7 +1930,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>MASTER INTEGRITY CHECK (0 = OK; cash viability reported separately)</t>
+          <t>MASTER INTEGRITY CHECK (0 = all tests pass)</t>
         </is>
       </c>
       <c r="B12" s="30">
@@ -1941,7 +1941,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>MONTHS WITH CASH BELOW ZERO (viability count)</t>
+          <t>MONTHS WITH CASH BELOW ZERO</t>
         </is>
       </c>
       <c r="B13" s="31">
@@ -1952,7 +1952,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>PEAK ADDITIONAL CAPITAL REQUIRED</t>
+          <t>PEAK ADDITIONAL FUNDING REQUIREMENT</t>
         </is>
       </c>
       <c r="B14" s="24">
@@ -2038,7 +2038,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KPI DASHBOARD - the rows a lender / investment committee reads first. All live links.</t>
+          <t>KPI DASHBOARD - key operating and coverage indicators. All cells are live links.</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>UNFUNDED NEED (additional capital required this month)</t>
+          <t>Additional funding requirement (this month)</t>
         </is>
       </c>
       <c r="C20" s="23">
@@ -5446,7 +5446,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3-YEAR SUMMARY - annual rollup; GLOBAL DSCR is the operative SBA test (per audit).</t>
+          <t>3-YEAR SUMMARY - annual rollup with per-year and global (3-year) debt-service coverage.</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Note: Y1 DSCR is structurally thin for a hospice startup (license maturation + Medicare payment cycle). Per the audit: lead with Global DSCR; do not force Y1 to 1.25x.</t>
+          <t>Note: Year-1 coverage reflects the startup ramp (license maturation and the Medicare payment cycle); the global 3-year DSCR is the appropriate coverage measure for the ramp period.</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6403,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CONTROL TOWER - every number in the model flows from this tab. Yellow = input; everything else is formulas.</t>
+          <t>CONTROL TOWER - all model inputs. Yellow cells are inputs; all other cells in the workbook are formulas.</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>BANK-REFI TOGGLE (1 = $500K/6%/36 funds Sept - BASE)</t>
+          <t>INTERIM BANK NOTE (1 = $500K/6%/36 funds Sept - base case)</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>BASE = 1: Bullard-relationship bank refi (confirmed) pays seller Sept; 0 = seller carried to Jan balloon per MIPA</t>
+          <t>Base case: interim bank note retires the seller balance in September; 0 = seller carried to the January balloon per the MIPA</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>SBA TOGGLE (1 = SBA 7(a) funds &amp; REFINANCES the bank note) - BASE</t>
+          <t>SBA 7(a) LOAN (1 = funds and refinances the bank note - base case)</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>SBA proceeds pay off the bank-refi balance at funding month</t>
+          <t>SBA proceeds retire the bank-note balance at the funding month</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CLINICAL LABOR  (Acct 4000; benefits/WC per audit)</t>
+          <t>CLINICAL LABOR  (Acct 4000; benefits and workers compensation loads)</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>post-audit: bottom of 22-28% band</t>
+          <t>industry range 22-28%; modeled at 22%</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>PRN PER-VISIT SUPPLEMENT  (1099; fires when FTE capacity &lt; required visits)</t>
+          <t>PRN PER-VISIT SUPPLEMENT  (1099; applies when FTE capacity is below required visits)</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>QAPI 0.5 FTE fires at ADC &gt;=</t>
+          <t>QAPI 0.5 FTE begins at ADC &gt;=</t>
         </is>
       </c>
       <c r="B94" s="9" t="n">
@@ -7553,7 +7553,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>G&amp;A  (MAX(fixed, % of net revenue) per audit pattern)</t>
+          <t>G&amp;A  (greater of fixed amount or % of net revenue)</t>
         </is>
       </c>
     </row>
@@ -7728,14 +7728,14 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>REAL-CASH DISCIPLINE (no revolver / no invented capital - shortfalls are SHOWN)</t>
+          <t>WORKING-CAPITAL POLICY (no revolving facility assumed; any funding requirement is stated explicitly)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>OWNER-DEFERRAL TOGGLE (1 = Silas/Dana/Brad defer to break-even)</t>
+          <t>MANAGEMENT SALARY DEFERRAL (1 = active)</t>
         </is>
       </c>
       <c r="B123" s="7" t="n">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>wages accrue on P&amp;L; cash paid once prior-month ADC &gt;= threshold; accrual repaid at repay month</t>
+          <t>three owner-operators defer salary until break-even census; wages accrue on the P&amp;L and are repaid at the repayment month</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>SELLER-DEFERRAL CONTINGENCY (1 = installments roll to Jan balloon)</t>
+          <t>SCENARIO: seller installment deferral (1 = installments roll to Jan balloon)</t>
         </is>
       </c>
       <c r="B129" s="7" t="n">
@@ -7823,14 +7823,14 @@
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>documented fallback - NOT base</t>
+          <t>contingency scenario; excluded from the base case</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>Investor notes raised (10% IO qtrly, 3-yr) - REAL ONLY</t>
+          <t>Investor notes (10% interest-only quarterly, 3-yr)</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>0 = none assumed; set only when checks clear</t>
+          <t>included only when subscribed; $0 in the base case</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>Cash warning threshold (reporting/formatting only)</t>
+          <t>Cash reporting threshold (display only)</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>no facility behind it - display only</t>
+          <t>presentation threshold; no credit facility is assumed</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>STAFFING - FTEs step with census (caseload formulas); PRN 1099 supplement fires when FTE capacity &lt; required visits.</t>
+          <t>STAFFING - FTEs scale with census on caseload ratios; PRN 1099 supplement covers visits above FTE capacity.</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>QAPI / Compliance 0.5 FTE (fires at ADC threshold)</t>
+          <t>QAPI / Compliance 0.5 FTE (begins at ADC threshold)</t>
         </is>
       </c>
       <c r="C30" s="22">
@@ -15693,14 +15693,14 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>OWNER DEFERRAL (Silas/Dana/Brad wages accrue until prior-month ADC &gt;= threshold; expense unchanged)</t>
+          <t>MANAGEMENT SALARY DEFERRAL (owner-operator wages accrue until break-even census; P&amp;L expense unchanged)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Deferral active this month (1 = accruing, not paying)</t>
+          <t>Deferral active this month (1 = wages accruing)</t>
         </is>
       </c>
       <c r="C41" s="12">
@@ -16384,7 +16384,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>OPERATING BUDGET - direct patient care per PD; facility (stepped rent); G&amp;A = MAX(fixed, % of NPR) per audit pattern.</t>
+          <t>OPERATING BUDGET - direct patient care per patient-day; facility (stepped rent); G&amp;A at the greater of fixed or % of revenue.</t>
         </is>
       </c>
     </row>
@@ -23534,7 +23534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CASH FLOW - collections timing + CHOW hold; payroll in month; DPC net-30; full debt schedules with toggles. Direct method.</t>
+          <t>CASH FLOW - collections timing and payment hold; payroll in month; patient-care costs net-30; complete debt schedules. Direct method.</t>
         </is>
       </c>
     </row>
@@ -25212,7 +25212,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DEBT - BALLOON REFI (auto when full-refi OFF) / FULL REFI / SBA (toggles)</t>
+          <t>DEBT - BALLOON REFINANCING / INTERIM BANK NOTE / SBA 7(a) (per scenario settings)</t>
         </is>
       </c>
     </row>
@@ -27358,7 +27358,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CASH (direct method; NO revolver - shortfalls are shown, not plugged)</t>
+          <t>CASH (direct method; no revolving facility assumed)</t>
         </is>
       </c>
     </row>
@@ -28422,7 +28422,7 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>ENDING CASH (may go NEGATIVE - that is the point)</t>
+          <t>ENDING CASH</t>
         </is>
       </c>
       <c r="C43" s="24">
@@ -28573,7 +28573,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>UNFUNDED NEED (cash below $0 - additional capital required)</t>
+          <t>ADDITIONAL FUNDING REQUIREMENT (amount by which cash is below zero)</t>
         </is>
       </c>
       <c r="C44" s="23">
@@ -28886,7 +28886,7 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PEAK ADDITIONAL CAPITAL REQUIRED (raise this much, or $0 = fully funded)</t>
+          <t>PEAK ADDITIONAL FUNDING REQUIREMENT ($0 = fully funded)</t>
         </is>
       </c>
       <c r="B47" s="24">
@@ -28983,7 +28983,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BALANCE SHEET - no plug cells; the check row must be zero in every month.</t>
+          <t>BALANCE SHEET - fully articulated (no balancing entries); the check row equals zero in every month.</t>
         </is>
       </c>
     </row>

--- a/financial_models/output/Azalea_Hospice_Proforma_Rev4.10_DYNAMIC.xlsx
+++ b/financial_models/output/Azalea_Hospice_Proforma_Rev4.10_DYNAMIC.xlsx
@@ -799,15 +799,15 @@
         </is>
       </c>
       <c r="C12" s="45">
-        <f>'3-Year Summary'!B5</f>
+        <f>'3-Year Summary'!B9</f>
         <v/>
       </c>
       <c r="D12" s="45">
-        <f>'3-Year Summary'!C5</f>
+        <f>'3-Year Summary'!C9</f>
         <v/>
       </c>
       <c r="E12" s="45">
-        <f>'3-Year Summary'!D5</f>
+        <f>'3-Year Summary'!D9</f>
         <v/>
       </c>
     </row>
@@ -818,15 +818,15 @@
         </is>
       </c>
       <c r="C13" s="45">
-        <f>'3-Year Summary'!B6</f>
+        <f>'3-Year Summary'!B21</f>
         <v/>
       </c>
       <c r="D13" s="45">
-        <f>'3-Year Summary'!C6</f>
+        <f>'3-Year Summary'!C21</f>
         <v/>
       </c>
       <c r="E13" s="45">
-        <f>'3-Year Summary'!D6</f>
+        <f>'3-Year Summary'!D21</f>
         <v/>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5446,7 +5446,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3-YEAR SUMMARY - annual rollup with per-year and global (3-year) debt-service coverage.</t>
+          <t>3-YEAR SUMMARY - annual rollup with full P&amp;L detail, year-end balance sheet, and per-year and global (3-year) debt-service coverage. Built for lender financial-spread tools.</t>
         </is>
       </c>
     </row>
@@ -5471,122 +5471,535 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Net patient revenue</t>
-        </is>
-      </c>
-      <c r="B5" s="23">
-        <f>SUM('P&amp;L'!C10:N10)</f>
-        <v/>
-      </c>
-      <c r="C5" s="23">
-        <f>SUM('P&amp;L'!O10:Z10)</f>
-        <v/>
-      </c>
-      <c r="D5" s="23">
-        <f>SUM('P&amp;L'!AA10:AL10)</f>
-        <v/>
+          <t>OPERATING RESULTS (annual)</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B6" s="23">
-        <f>SUM('P&amp;L'!C24:N24)</f>
-        <v/>
-      </c>
-      <c r="C6" s="23">
-        <f>SUM('P&amp;L'!O24:Z24)</f>
-        <v/>
-      </c>
-      <c r="D6" s="23">
-        <f>SUM('P&amp;L'!AA24:AL24)</f>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Average daily census (year average)</t>
+        </is>
+      </c>
+      <c r="B6" s="18">
+        <f>AVERAGE('Census Waterfall'!C11:N11)</f>
+        <v/>
+      </c>
+      <c r="C6" s="18">
+        <f>AVERAGE('Census Waterfall'!O11:Z11)</f>
+        <v/>
+      </c>
+      <c r="D6" s="18">
+        <f>AVERAGE('Census Waterfall'!AA11:AL11)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t>Gross patient revenue</t>
         </is>
       </c>
       <c r="B7" s="22">
-        <f>SUM('Cash Flow &amp; Runway'!C34:N34)</f>
+        <f>SUM('P&amp;L'!C8:N8)</f>
         <v/>
       </c>
       <c r="C7" s="22">
-        <f>SUM('Cash Flow &amp; Runway'!O34:Z34)</f>
+        <f>SUM('P&amp;L'!O8:Z8)</f>
         <v/>
       </c>
       <c r="D7" s="22">
-        <f>SUM('Cash Flow &amp; Runway'!AA34:AL34)</f>
+        <f>SUM('P&amp;L'!AA8:AL8)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Debt service (P&amp;I, all notes)</t>
+          <t>Deductions &amp; billing fees</t>
         </is>
       </c>
       <c r="B8" s="22">
-        <f>SUM('Cash Flow &amp; Runway'!C19:N19)+SUM('Cash Flow &amp; Runway'!C22:N22)+SUM('Cash Flow &amp; Runway'!C25:N25)+SUM('Cash Flow &amp; Runway'!C14:N14)+SUM('Cash Flow &amp; Runway'!C15:N15)</f>
+        <f>SUM('P&amp;L'!C9:N9)</f>
         <v/>
       </c>
       <c r="C8" s="22">
-        <f>SUM('Cash Flow &amp; Runway'!O19:Z19)+SUM('Cash Flow &amp; Runway'!O22:Z22)+SUM('Cash Flow &amp; Runway'!O25:Z25)+SUM('Cash Flow &amp; Runway'!O14:Z14)+SUM('Cash Flow &amp; Runway'!O15:Z15)</f>
+        <f>SUM('P&amp;L'!O9:Z9)</f>
         <v/>
       </c>
       <c r="D8" s="22">
-        <f>SUM('Cash Flow &amp; Runway'!AA19:AL19)+SUM('Cash Flow &amp; Runway'!AA22:AL22)+SUM('Cash Flow &amp; Runway'!AA25:AL25)+SUM('Cash Flow &amp; Runway'!AA14:AL14)+SUM('Cash Flow &amp; Runway'!AA15:AL15)</f>
+        <f>SUM('P&amp;L'!AA9:AL9)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
+          <t>Net patient revenue</t>
+        </is>
+      </c>
+      <c r="B9" s="23">
+        <f>SUM('P&amp;L'!C10:N10)</f>
+        <v/>
+      </c>
+      <c r="C9" s="23">
+        <f>SUM('P&amp;L'!O10:Z10)</f>
+        <v/>
+      </c>
+      <c r="D9" s="23">
+        <f>SUM('P&amp;L'!AA10:AL10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Direct patient care costs</t>
+        </is>
+      </c>
+      <c r="B10" s="22">
+        <f>SUM('P&amp;L'!C12:N12)</f>
+        <v/>
+      </c>
+      <c r="C10" s="22">
+        <f>SUM('P&amp;L'!O12:Z12)</f>
+        <v/>
+      </c>
+      <c r="D10" s="22">
+        <f>SUM('P&amp;L'!AA12:AL12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Clinical labor &amp; benefits</t>
+        </is>
+      </c>
+      <c r="B11" s="22">
+        <f>SUM('P&amp;L'!C13:N13)</f>
+        <v/>
+      </c>
+      <c r="C11" s="22">
+        <f>SUM('P&amp;L'!O13:Z13)</f>
+        <v/>
+      </c>
+      <c r="D11" s="22">
+        <f>SUM('P&amp;L'!AA13:AL13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Total cost of services</t>
+        </is>
+      </c>
+      <c r="B12" s="22">
+        <f>SUM('P&amp;L'!C14:N14)</f>
+        <v/>
+      </c>
+      <c r="C12" s="22">
+        <f>SUM('P&amp;L'!O14:Z14)</f>
+        <v/>
+      </c>
+      <c r="D12" s="22">
+        <f>SUM('P&amp;L'!AA14:AL14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B13" s="23">
+        <f>SUM('P&amp;L'!C15:N15)</f>
+        <v/>
+      </c>
+      <c r="C13" s="23">
+        <f>SUM('P&amp;L'!O15:Z15)</f>
+        <v/>
+      </c>
+      <c r="D13" s="23">
+        <f>SUM('P&amp;L'!AA15:AL15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B14" s="11">
+        <f>IF(B9=0,"-",B13/B9)</f>
+        <v/>
+      </c>
+      <c r="C14" s="11">
+        <f>IF(C9=0,"-",C13/C9)</f>
+        <v/>
+      </c>
+      <c r="D14" s="11">
+        <f>IF(D9=0,"-",D13/D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Indirect / administrative labor</t>
+        </is>
+      </c>
+      <c r="B15" s="22">
+        <f>SUM('P&amp;L'!C18:N18)</f>
+        <v/>
+      </c>
+      <c r="C15" s="22">
+        <f>SUM('P&amp;L'!O18:Z18)</f>
+        <v/>
+      </c>
+      <c r="D15" s="22">
+        <f>SUM('P&amp;L'!AA18:AL18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Facility costs</t>
+        </is>
+      </c>
+      <c r="B16" s="22">
+        <f>SUM('P&amp;L'!C19:N19)</f>
+        <v/>
+      </c>
+      <c r="C16" s="22">
+        <f>SUM('P&amp;L'!O19:Z19)</f>
+        <v/>
+      </c>
+      <c r="D16" s="22">
+        <f>SUM('P&amp;L'!AA19:AL19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>G&amp;A - other</t>
+        </is>
+      </c>
+      <c r="B17" s="22">
+        <f>SUM('P&amp;L'!C20:N20)</f>
+        <v/>
+      </c>
+      <c r="C17" s="22">
+        <f>SUM('P&amp;L'!O20:Z20)</f>
+        <v/>
+      </c>
+      <c r="D17" s="22">
+        <f>SUM('P&amp;L'!AA20:AL20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; amortization</t>
+        </is>
+      </c>
+      <c r="B18" s="22">
+        <f>SUM('P&amp;L'!C21:N21)</f>
+        <v/>
+      </c>
+      <c r="C18" s="22">
+        <f>SUM('P&amp;L'!O21:Z21)</f>
+        <v/>
+      </c>
+      <c r="D18" s="22">
+        <f>SUM('P&amp;L'!AA21:AL21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="B19" s="22">
+        <f>SUM('P&amp;L'!C22:N22)</f>
+        <v/>
+      </c>
+      <c r="C19" s="22">
+        <f>SUM('P&amp;L'!O22:Z22)</f>
+        <v/>
+      </c>
+      <c r="D19" s="22">
+        <f>SUM('P&amp;L'!AA22:AL22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B20" s="22">
+        <f>SUM('P&amp;L'!C23:N23)</f>
+        <v/>
+      </c>
+      <c r="C20" s="22">
+        <f>SUM('P&amp;L'!O23:Z23)</f>
+        <v/>
+      </c>
+      <c r="D20" s="22">
+        <f>SUM('P&amp;L'!AA23:AL23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B21" s="23">
+        <f>SUM('P&amp;L'!C24:N24)</f>
+        <v/>
+      </c>
+      <c r="C21" s="23">
+        <f>SUM('P&amp;L'!O24:Z24)</f>
+        <v/>
+      </c>
+      <c r="D21" s="23">
+        <f>SUM('P&amp;L'!AA24:AL24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="B22" s="33">
+        <f>IF(B9=0,"-",B21/B9)</f>
+        <v/>
+      </c>
+      <c r="C22" s="33">
+        <f>IF(C9=0,"-",C21/C9)</f>
+        <v/>
+      </c>
+      <c r="D22" s="33">
+        <f>IF(D9=0,"-",D21/D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Contingency provision (below EBITDA, non-GAAP buffer)</t>
+        </is>
+      </c>
+      <c r="B23" s="22">
+        <f>SUM('P&amp;L'!C26:N26)</f>
+        <v/>
+      </c>
+      <c r="C23" s="22">
+        <f>SUM('P&amp;L'!O26:Z26)</f>
+        <v/>
+      </c>
+      <c r="D23" s="22">
+        <f>SUM('P&amp;L'!AA26:AL26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="B24" s="22">
+        <f>SUM('Cash Flow &amp; Runway'!C34:N34)</f>
+        <v/>
+      </c>
+      <c r="C24" s="22">
+        <f>SUM('Cash Flow &amp; Runway'!O34:Z34)</f>
+        <v/>
+      </c>
+      <c r="D24" s="22">
+        <f>SUM('Cash Flow &amp; Runway'!AA34:AL34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>YEAR-END BALANCE SHEET (snapshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="B27" s="22">
+        <f>'Balance Sheet'!N6</f>
+        <v/>
+      </c>
+      <c r="C27" s="22">
+        <f>'Balance Sheet'!Z6</f>
+        <v/>
+      </c>
+      <c r="D27" s="22">
+        <f>'Balance Sheet'!AL6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="B28" s="22">
+        <f>'Balance Sheet'!N7</f>
+        <v/>
+      </c>
+      <c r="C28" s="22">
+        <f>'Balance Sheet'!Z7</f>
+        <v/>
+      </c>
+      <c r="D28" s="22">
+        <f>'Balance Sheet'!AL7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B29" s="23">
+        <f>'Balance Sheet'!N10</f>
+        <v/>
+      </c>
+      <c r="C29" s="23">
+        <f>'Balance Sheet'!Z10</f>
+        <v/>
+      </c>
+      <c r="D29" s="23">
+        <f>'Balance Sheet'!AL10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="22">
+        <f>'Balance Sheet'!N18</f>
+        <v/>
+      </c>
+      <c r="C30" s="22">
+        <f>'Balance Sheet'!Z18</f>
+        <v/>
+      </c>
+      <c r="D30" s="22">
+        <f>'Balance Sheet'!AL18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B31" s="23">
+        <f>'Balance Sheet'!N19+'Balance Sheet'!N20</f>
+        <v/>
+      </c>
+      <c r="C31" s="23">
+        <f>'Balance Sheet'!Z19+'Balance Sheet'!Z20</f>
+        <v/>
+      </c>
+      <c r="D31" s="23">
+        <f>'Balance Sheet'!AL19+'Balance Sheet'!AL20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Debt service (P&amp;I, all notes)</t>
+        </is>
+      </c>
+      <c r="B33" s="22">
+        <f>SUM('Cash Flow &amp; Runway'!C19:N19)+SUM('Cash Flow &amp; Runway'!C22:N22)+SUM('Cash Flow &amp; Runway'!C25:N25)+SUM('Cash Flow &amp; Runway'!C14:N14)+SUM('Cash Flow &amp; Runway'!C15:N15)</f>
+        <v/>
+      </c>
+      <c r="C33" s="22">
+        <f>SUM('Cash Flow &amp; Runway'!O19:Z19)+SUM('Cash Flow &amp; Runway'!O22:Z22)+SUM('Cash Flow &amp; Runway'!O25:Z25)+SUM('Cash Flow &amp; Runway'!O14:Z14)+SUM('Cash Flow &amp; Runway'!O15:Z15)</f>
+        <v/>
+      </c>
+      <c r="D33" s="22">
+        <f>SUM('Cash Flow &amp; Runway'!AA19:AL19)+SUM('Cash Flow &amp; Runway'!AA22:AL22)+SUM('Cash Flow &amp; Runway'!AA25:AL25)+SUM('Cash Flow &amp; Runway'!AA14:AL14)+SUM('Cash Flow &amp; Runway'!AA15:AL15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
           <t>DSCR (per year)</t>
         </is>
       </c>
-      <c r="B9" s="34">
-        <f>IF(B8=0,"-",B6/B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="34">
-        <f>IF(C8=0,"-",C6/C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="34">
-        <f>IF(D8=0,"-",D6/D8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="B34" s="34">
+        <f>IF(B33=0,"-",B21/B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="34">
+        <f>IF(C33=0,"-",C21/C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="34">
+        <f>IF(D33=0,"-",D21/D33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>GLOBAL 3-YEAR DSCR (operative SBA test)</t>
         </is>
       </c>
-      <c r="B11" s="35">
-        <f>SUM(B6:D6)/SUM(B8:D8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="B36" s="35">
+        <f>SUM(B21:D21)/SUM(B33:D33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Minimum cash across 36 months</t>
         </is>
       </c>
-      <c r="B12" s="23">
+      <c r="B37" s="23">
         <f>'Cash Flow &amp; Runway'!B46</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Note: Year-1 coverage reflects the startup ramp (license maturation and the Medicare payment cycle); the global 3-year DSCR is the appropriate coverage measure for the ramp period.</t>
         </is>
